--- a/排课结果/静默跳过课程统计.xlsx
+++ b/排课结果/静默跳过课程统计.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,15 +452,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>16.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ZXS=0(周学时为0)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2.6%</t>
         </is>
       </c>
     </row>
@@ -563,7 +578,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -598,7 +613,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时16÷上课周数1，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -656,7 +671,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -714,7 +729,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -772,7 +787,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -830,7 +845,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -888,7 +903,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -946,7 +961,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1019,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1077,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1135,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1193,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1251,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1309,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1367,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1425,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1483,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1541,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1599,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1657,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1715,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1773,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1831,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1889,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1947,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -1990,7 +2005,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2063,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2179,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2237,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2295,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2353,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2411,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2469,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2527,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2585,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2643,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2701,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2759,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2817,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2875,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2933,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2991,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3049,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3107,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3165,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3223,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3281,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3339,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3397,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3455,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3513,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3571,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3629,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3687,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3745,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3803,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3861,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3919,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3977,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4035,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4093,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4151,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4209,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4267,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4325,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4383,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -4426,7 +4441,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4499,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4557,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4615,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4673,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4731,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4789,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -4832,7 +4847,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4905,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4963,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5021,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5079,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5137,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -5180,7 +5195,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5253,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5311,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5369,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5427,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5485,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5543,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5601,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5659,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5717,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5775,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5833,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5891,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5949,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -5992,7 +6007,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6065,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6123,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6181,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6239,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6297,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -6340,7 +6355,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6413,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6471,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6529,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6587,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6645,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6703,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6761,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6819,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -6862,7 +6877,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6935,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6993,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7051,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -7094,7 +7109,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -7152,7 +7167,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7225,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7283,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7341,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7399,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7457,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -7500,7 +7515,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7573,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7631,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7689,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7747,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7805,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7863,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7921,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -7964,7 +7979,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -8022,7 +8037,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8095,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8153,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8211,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8269,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -8312,7 +8327,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8385,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -8428,7 +8443,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8501,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8559,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8617,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -8660,7 +8675,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8733,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8791,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -8834,7 +8849,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8907,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -8950,7 +8965,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -9008,7 +9023,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9081,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9139,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9197,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -9240,7 +9255,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9313,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9371,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9429,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9487,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9545,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9603,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -9646,7 +9661,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -9704,7 +9719,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -9762,7 +9777,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9835,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -9878,7 +9893,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -9936,7 +9951,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -9994,7 +10009,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10067,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10125,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10183,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10241,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -10284,7 +10299,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -10342,7 +10357,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -10400,7 +10415,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -10458,7 +10473,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -10516,7 +10531,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -10574,7 +10589,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10647,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -10690,7 +10705,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -10748,7 +10763,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10821,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -10864,7 +10879,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -10922,7 +10937,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -10980,7 +10995,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11053,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -11096,7 +11111,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -11154,7 +11169,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11227,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -11270,7 +11285,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11343,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -11386,7 +11401,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -11444,7 +11459,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -11502,7 +11517,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -11560,7 +11575,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -11618,7 +11633,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11691,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11749,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -11792,7 +11807,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -11850,7 +11865,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -11908,7 +11923,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -11966,7 +11981,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -12024,7 +12039,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -12082,7 +12097,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -12140,7 +12155,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12213,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12267,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -12306,7 +12321,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -12360,7 +12375,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -12414,7 +12429,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -12468,7 +12483,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -12522,7 +12537,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -12576,7 +12591,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -12630,7 +12645,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -12684,7 +12699,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -12738,7 +12753,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -12792,7 +12807,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -12846,7 +12861,7 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -12900,7 +12915,7 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -12954,7 +12969,7 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13008,7 +13023,7 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13062,7 +13077,7 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13116,7 +13131,7 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13170,7 +13185,7 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13224,7 +13239,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13293,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13332,7 +13347,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13386,7 +13401,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13440,7 +13455,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13509,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13548,7 +13563,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13617,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13656,7 +13671,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13710,7 +13725,7 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13764,7 +13779,7 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13818,7 +13833,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13872,7 +13887,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13926,7 +13941,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -13980,7 +13995,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -14038,7 +14053,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -14096,7 +14111,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -14154,7 +14169,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -14212,7 +14227,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -14270,7 +14285,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -14328,7 +14343,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -14386,7 +14401,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -14444,7 +14459,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14517,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -14560,7 +14575,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -14618,7 +14633,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -14676,7 +14691,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14749,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -14792,7 +14807,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -14850,7 +14865,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -14908,7 +14923,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -14966,7 +14981,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15039,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15097,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -15140,7 +15155,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -15198,7 +15213,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -15256,7 +15271,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -15283,7 +15298,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -15318,7 +15333,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>ZXS=18 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=18=学时270÷上课周数15，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -15345,7 +15360,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -15380,7 +15395,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>ZXS=18 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=18=学时270÷上课周数15，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -15407,7 +15422,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -15442,7 +15457,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>ZXS=18 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=18=学时270÷上课周数15，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -15469,7 +15484,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -15504,7 +15519,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>ZXS=18 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=18=学时270÷上课周数15，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -15562,7 +15577,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -15620,7 +15635,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -15678,7 +15693,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -15736,7 +15751,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -15763,7 +15778,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -15798,7 +15813,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -15825,7 +15840,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -15860,7 +15875,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -15887,7 +15902,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -15922,7 +15937,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -15949,7 +15964,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -15984,7 +15999,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>ZXS=12 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=12=学时48÷上课周数4，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -16011,7 +16026,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -16046,7 +16061,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>ZXS=12 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=12=学时48÷上课周数4，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -16073,7 +16088,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -16108,7 +16123,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>ZXS=12 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=12=学时48÷上课周数4，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -16135,7 +16150,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -16170,7 +16185,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>ZXS=10.5 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=10.5=学时32÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -16197,7 +16212,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -16232,7 +16247,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>ZXS=10.5 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=10.5=学时32÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -16259,7 +16274,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -16294,7 +16309,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>ZXS=10.5 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=10.5=学时32÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -16321,7 +16336,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -16356,7 +16371,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时32÷上课周数2，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -16383,7 +16398,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -16418,7 +16433,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时32÷上课周数2，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -16445,7 +16460,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -16480,7 +16495,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时32÷上课周数2，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -16507,7 +16522,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -16542,7 +16557,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -16569,7 +16584,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -16604,7 +16619,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -16631,7 +16646,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -16666,7 +16681,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -16693,7 +16708,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -16728,7 +16743,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时32÷上课周数2，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -16755,7 +16770,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -16790,7 +16805,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时32÷上课周数2，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16832,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -16852,7 +16867,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时32÷上课周数2，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -16879,7 +16894,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -16914,7 +16929,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16956,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -16976,7 +16991,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17018,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -17038,7 +17053,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -17065,7 +17080,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -17100,7 +17115,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>ZXS=12 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=12=学时48÷上课周数4，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -17127,7 +17142,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -17162,7 +17177,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>ZXS=12 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=12=学时48÷上课周数4，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -17189,7 +17204,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -17224,7 +17239,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>ZXS=12 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=12=学时48÷上课周数4，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -17251,7 +17266,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -17286,7 +17301,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -17313,7 +17328,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -17348,7 +17363,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -17375,7 +17390,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -17410,7 +17425,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -17437,7 +17452,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -17472,7 +17487,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -17499,7 +17514,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -17534,7 +17549,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -17561,7 +17576,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -17596,7 +17611,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -17623,7 +17638,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -17658,7 +17673,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>ZXS=12 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=12=学时48÷上课周数4，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -17685,7 +17700,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -17720,7 +17735,7 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>ZXS=12 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=12=学时48÷上课周数4，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -17747,7 +17762,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -17782,7 +17797,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>ZXS=12 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=12=学时48÷上课周数4，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -17809,7 +17824,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -17844,7 +17859,7 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -17871,7 +17886,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -17906,7 +17921,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -17933,7 +17948,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -17968,7 +17983,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -17995,7 +18010,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -18030,7 +18045,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -18057,7 +18072,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -18092,7 +18107,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -18119,7 +18134,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -18154,7 +18169,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -18181,7 +18196,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -18216,7 +18231,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>ZXS=12 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=12=学时48÷上课周数4，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -18243,7 +18258,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -18278,7 +18293,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>ZXS=12 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=12=学时48÷上课周数4，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18320,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -18340,7 +18355,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>ZXS=12 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=12=学时48÷上课周数4，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -18367,7 +18382,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -18402,7 +18417,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -18429,7 +18444,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -18464,7 +18479,7 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -18491,7 +18506,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -18526,7 +18541,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -18553,7 +18568,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -18588,7 +18603,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时64÷上课周数4，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -18615,7 +18630,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -18650,7 +18665,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时64÷上课周数4，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -18677,7 +18692,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -18712,7 +18727,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -18739,7 +18754,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -18774,7 +18789,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -18801,7 +18816,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -18836,7 +18851,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时48÷上课周数3，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -18894,7 +18909,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -18952,7 +18967,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -19010,7 +19025,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -19068,7 +19083,7 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -19126,7 +19141,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -19184,7 +19199,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -19242,7 +19257,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -19300,7 +19315,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -19358,7 +19373,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -19385,7 +19400,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -19420,7 +19435,7 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时16÷上课周数1，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -19447,7 +19462,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>短周次集中授课(ZXS&gt;8)</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -19482,7 +19497,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>ZXS=16 超出[1,8]，疑似把「总学时」误填入「周学时」列——需教务核实换算</t>
+          <t>短周次集中授课：ZXS=16=学时16÷上课周数1，计算正确，非误填。被过滤是因排课算法只支持每周≤8节(ZXS∈[1,8])——属算法能力边界。如需排课：算法需支持高周学时，或将集中课按周拆分</t>
         </is>
       </c>
     </row>
@@ -19509,7 +19524,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>ZXS=0(周学时为0)</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -19544,7 +19559,7 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>ZXS=0(周学时为0)，无法生成课时——需教务核实该课是否上课及周学时</t>
+          <t>ZXS=0(周学时为0)——需教务核实该课是否开课及周学时</t>
         </is>
       </c>
     </row>
@@ -19571,7 +19586,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>ZXS=0(周学时为0)</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -19606,7 +19621,7 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>ZXS=0(周学时为0)，无法生成课时——需教务核实该课是否上课及周学时</t>
+          <t>ZXS=0(周学时为0)——需教务核实该课是否开课及周学时</t>
         </is>
       </c>
     </row>
@@ -19633,7 +19648,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>ZXS=0(周学时为0)</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -19668,7 +19683,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>ZXS=0(周学时为0)，无法生成课时——需教务核实该课是否上课及周学时</t>
+          <t>ZXS=0(周学时为0)——需教务核实该课是否开课及周学时</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19710,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>ZXS=0(周学时为0)</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -19730,7 +19745,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>ZXS=0(周学时为0)，无法生成课时——需教务核实该课是否上课及周学时</t>
+          <t>ZXS=0(周学时为0)——需教务核实该课是否开课及周学时</t>
         </is>
       </c>
     </row>
@@ -19757,7 +19772,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>ZXS=0(周学时为0)</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -19792,7 +19807,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>ZXS=0(周学时为0)，无法生成课时——需教务核实该课是否上课及周学时</t>
+          <t>ZXS=0(周学时为0)——需教务核实该课是否开课及周学时</t>
         </is>
       </c>
     </row>
@@ -19819,7 +19834,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>ZXS=0(周学时为0)</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -19854,7 +19869,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>ZXS=0(周学时为0)，无法生成课时——需教务核实该课是否上课及周学时</t>
+          <t>ZXS=0(周学时为0)——需教务核实该课是否开课及周学时</t>
         </is>
       </c>
     </row>
@@ -19881,7 +19896,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>ZXS=0(周学时为0)</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -19916,7 +19931,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>ZXS=0(周学时为0)，无法生成课时——需教务核实该课是否上课及周学时</t>
+          <t>ZXS=0(周学时为0)——需教务核实该课是否开课及周学时</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19958,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>ZXS=0(周学时为0)</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -19978,7 +19993,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>ZXS=0(周学时为0)，无法生成课时——需教务核实该课是否上课及周学时</t>
+          <t>ZXS=0(周学时为0)——需教务核实该课是否开课及周学时</t>
         </is>
       </c>
     </row>
@@ -20005,7 +20020,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>周学时ZXS非法</t>
+          <t>ZXS=0(周学时为0)</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -20040,7 +20055,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>ZXS=0(周学时为0)，无法生成课时——需教务核实该课是否上课及周学时</t>
+          <t>ZXS=0(周学时为0)——需教务核实该课是否开课及周学时</t>
         </is>
       </c>
     </row>
@@ -20098,7 +20113,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -20156,7 +20171,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -20214,7 +20229,7 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -20272,7 +20287,7 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -20330,7 +20345,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
@@ -20388,7 +20403,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>教务标注「不需要排课」(SFXYPK=0)——多为体育/物理实验等，属正常跳过；若应排需教务改 SFXYPK=1</t>
+          <t>教务标注「不需要排课」(SFXYPK=0)——多为物理实验/体育等，属正常跳过；若应排需教务改 SFXYPK=1</t>
         </is>
       </c>
     </row>
